--- a/01_Thermal/B_results/Single_Fan_GP/single_gp_summary.xlsx
+++ b/01_Thermal/B_results/Single_Fan_GP/single_gp_summary.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,15 +469,20 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>feature_mode</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>use_radial_features</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>log_marginal_likelihood</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>kernel</t>
         </is>
@@ -488,35 +493,40 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.06686371167524949</v>
+        <v>0.03803914972487243</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2319093134254427</v>
+        <v>0.1187966915811342</v>
       </c>
       <c r="D2" t="n">
-        <v>91.26896643671554</v>
+        <v>51.92343937445087</v>
       </c>
       <c r="E2" t="n">
-        <v>73.4123339769732</v>
+        <v>19.26377261530057</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1731110873539931</v>
+        <v>0.06516331124277358</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8480354806684861</v>
+        <v>0.9601237314302804</v>
       </c>
       <c r="H2" t="n">
         <v>1365</v>
       </c>
-      <c r="I2" t="b">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
+      </c>
+      <c r="J2" t="b">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>-1042.675284264143</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.744**2 * RBF(length_scale=[0.117, 0.194, 6.17]) + WhiteKernel(noise_level=0.132)</t>
+      <c r="K2" t="n">
+        <v>-246.847471403069</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.23**2 * RBF(length_scale=[0.141, 3.97, 19.9, 0.288]) + WhiteKernel(noise_level=0.00664)</t>
         </is>
       </c>
     </row>
@@ -602,25 +612,25 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.102216779809836</v>
+        <v>0.0272626215455659</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3615243603878376</v>
+        <v>0.07371661888439368</v>
       </c>
       <c r="G2" t="n">
-        <v>19.93227206291802</v>
+        <v>5.316211201385351</v>
       </c>
       <c r="H2" t="n">
-        <v>25.48647331499784</v>
+        <v>1.059657280450655</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4574212170103216</v>
+        <v>0.05611123567304827</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7521697111277293</v>
+        <v>0.9896958999907943</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2393412891192192</v>
+        <v>0.07739825573960134</v>
       </c>
     </row>
     <row r="3">
@@ -639,25 +649,25 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08224205377155676</v>
+        <v>0.03666216046636091</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2674208096681707</v>
+        <v>0.1112256906938555</v>
       </c>
       <c r="G3" t="n">
-        <v>16.03720048545357</v>
+        <v>7.149121290940379</v>
       </c>
       <c r="H3" t="n">
-        <v>13.9452084414981</v>
+        <v>2.412375082713418</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1373566017815918</v>
+        <v>0.06264973332930582</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8527552394084337</v>
+        <v>0.974528197767617</v>
       </c>
       <c r="K3" t="n">
-        <v>0.236927722826763</v>
+        <v>0.07243483532147664</v>
       </c>
     </row>
     <row r="4">
@@ -676,25 +686,25 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08184892964484289</v>
+        <v>0.03563005653844309</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2993083124036229</v>
+        <v>0.1014877139362925</v>
       </c>
       <c r="G4" t="n">
-        <v>15.96054128074436</v>
+        <v>6.947861024996403</v>
       </c>
       <c r="H4" t="n">
-        <v>17.46916584541142</v>
+        <v>2.008452435602874</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3268042616335176</v>
+        <v>0.08172831157172519</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7928061112676772</v>
+        <v>0.9761786524812363</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2350496411120093</v>
+        <v>0.07309611938448095</v>
       </c>
     </row>
     <row r="5">
@@ -713,25 +723,25 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05095226325330279</v>
+        <v>0.04706414832257115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1709855573988896</v>
+        <v>0.1547627704703274</v>
       </c>
       <c r="G5" t="n">
-        <v>9.935691334394043</v>
+        <v>9.177508922901374</v>
       </c>
       <c r="H5" t="n">
-        <v>5.70103186360675</v>
+        <v>4.670545449111994</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06534230898359385</v>
+        <v>0.05704789313606046</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9160725637845269</v>
+        <v>0.931242814520278</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2331334311209098</v>
+        <v>0.06447368587794437</v>
       </c>
     </row>
     <row r="6">
@@ -750,25 +760,25 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05940408030604913</v>
+        <v>0.05209262101113771</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1627721412884576</v>
+        <v>0.1753198600162836</v>
       </c>
       <c r="G6" t="n">
-        <v>11.58379565967958</v>
+        <v>10.15806109717185</v>
       </c>
       <c r="H6" t="n">
-        <v>5.166480146027773</v>
+        <v>5.993725396645205</v>
       </c>
       <c r="I6" t="n">
-        <v>0.102848838829091</v>
+        <v>0.09796183476908378</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8880888465568575</v>
+        <v>0.870169882860048</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2330135919763815</v>
+        <v>0.07044198382848003</v>
       </c>
     </row>
     <row r="7">
@@ -787,25 +797,25 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04174780615965168</v>
+        <v>0.03447844529976481</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1251469392496207</v>
+        <v>0.1049981771789993</v>
       </c>
       <c r="G7" t="n">
-        <v>8.140822201132078</v>
+        <v>6.723296833454137</v>
       </c>
       <c r="H7" t="n">
-        <v>3.054042498691909</v>
+        <v>2.149800356127943</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1180027175481368</v>
+        <v>0.08742295883459626</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9399994069194304</v>
+        <v>0.9577644068713045</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2378555304843354</v>
+        <v>0.08988010341484653</v>
       </c>
     </row>
     <row r="8">
@@ -824,25 +834,25 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0496340687815072</v>
+        <v>0.03308399489026344</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1152462662332923</v>
+        <v>0.07050064973872198</v>
       </c>
       <c r="G8" t="n">
-        <v>9.678643412393903</v>
+        <v>6.451379003601372</v>
       </c>
       <c r="H8" t="n">
-        <v>2.589931866739402</v>
+        <v>0.9692166146484824</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06497669868203118</v>
+        <v>0.04744876434512554</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9281063381302419</v>
+        <v>0.9730956121020226</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2506224604280322</v>
+        <v>0.06964840425919791</v>
       </c>
     </row>
   </sheetData>
@@ -856,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,11 +941,13 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>use_radial_features</t>
-        </is>
-      </c>
-      <c r="C6" t="b">
-        <v>0</v>
+          <t>feature_mode</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -944,11 +956,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sigma_fallback_mps</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.14</v>
+          <t>use_radial_features</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -957,11 +969,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sigma_min_mps</t>
+          <t>sigma_fallback_mps</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="9">
@@ -970,11 +982,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>n_restarts_optimizer</t>
+          <t>sigma_min_mps</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -983,11 +995,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>random_state</t>
+          <t>n_restarts_optimizer</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -996,12 +1008,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>random_state</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>kernel_fitted</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.744**2 * RBF(length_scale=[0.117, 0.194, 6.17]) + WhiteKernel(noise_level=0.132)</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.23**2 * RBF(length_scale=[0.141, 3.97, 19.9, 0.288]) + WhiteKernel(noise_level=0.00664)</t>
         </is>
       </c>
     </row>
@@ -1074,16 +1099,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>19.93227206291802</v>
+        <v>5.316211201385351</v>
       </c>
       <c r="E2" t="n">
-        <v>25.48647331499784</v>
+        <v>1.059657280450655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4574212170103216</v>
+        <v>0.05611123567304827</v>
       </c>
       <c r="G2" t="n">
-        <v>2511.573847332075</v>
+        <v>37.7931427287662</v>
       </c>
       <c r="H2" t="n">
         <v>12003.65050354092</v>
@@ -1102,16 +1127,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>16.03720048545357</v>
+        <v>7.149121290940379</v>
       </c>
       <c r="E3" t="n">
-        <v>13.9452084414981</v>
+        <v>2.412375082713418</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1373566017815918</v>
+        <v>0.06264973332930582</v>
       </c>
       <c r="G3" t="n">
-        <v>184.9552443677061</v>
+        <v>38.47742745768466</v>
       </c>
       <c r="H3" t="n">
         <v>9803.193489796933</v>
@@ -1130,16 +1155,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>15.96054128074436</v>
+        <v>6.947861024996403</v>
       </c>
       <c r="E4" t="n">
-        <v>17.46916584541142</v>
+        <v>2.008452435602874</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3268042616335176</v>
+        <v>0.08172831157172519</v>
       </c>
       <c r="G4" t="n">
-        <v>970.9247904152544</v>
+        <v>60.72327988049094</v>
       </c>
       <c r="H4" t="n">
         <v>9090.968804657296</v>
@@ -1158,16 +1183,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>9.935691334394043</v>
+        <v>9.177508922901374</v>
       </c>
       <c r="E5" t="n">
-        <v>5.70103186360675</v>
+        <v>4.670545449111994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06534230898359385</v>
+        <v>0.05704789313606046</v>
       </c>
       <c r="G5" t="n">
-        <v>305.8787993476448</v>
+        <v>233.1522670704965</v>
       </c>
       <c r="H5" t="n">
         <v>71640.79933933762</v>
@@ -1186,16 +1211,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>11.58379565967958</v>
+        <v>10.15806109717185</v>
       </c>
       <c r="E6" t="n">
-        <v>5.166480146027773</v>
+        <v>5.993725396645205</v>
       </c>
       <c r="F6" t="n">
-        <v>0.102848838829091</v>
+        <v>0.09796183476908378</v>
       </c>
       <c r="G6" t="n">
-        <v>169.73978431334</v>
+        <v>153.9921851038078</v>
       </c>
       <c r="H6" t="n">
         <v>16046.66774128612</v>
@@ -1214,16 +1239,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>8.140822201132078</v>
+        <v>6.723296833454137</v>
       </c>
       <c r="E7" t="n">
-        <v>3.054042498691909</v>
+        <v>2.149800356127943</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1180027175481368</v>
+        <v>0.08742295883459626</v>
       </c>
       <c r="G7" t="n">
-        <v>75.2495531803529</v>
+        <v>41.30198358019971</v>
       </c>
       <c r="H7" t="n">
         <v>5404.056829595331</v>
@@ -1242,16 +1267,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>9.678643412393903</v>
+        <v>6.451379003601372</v>
       </c>
       <c r="E8" t="n">
-        <v>2.589931866739402</v>
+        <v>0.9692166146484824</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06497669868203118</v>
+        <v>0.04744876434512554</v>
       </c>
       <c r="G8" t="n">
-        <v>82.43358210172131</v>
+        <v>43.95807870632481</v>
       </c>
       <c r="H8" t="n">
         <v>19524.90314262348</v>
@@ -1268,16 +1293,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>91.26896643671554</v>
+        <v>51.92343937445087</v>
       </c>
       <c r="E9" t="n">
-        <v>73.4123339769732</v>
+        <v>19.26377261530057</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1731110873539931</v>
+        <v>0.06516331124277359</v>
       </c>
       <c r="G9" t="n">
-        <v>4300.755601058096</v>
+        <v>609.3983645277706</v>
       </c>
       <c r="H9" t="n">
         <v>143514.2398508377</v>

--- a/01_Thermal/B_results/Single_Fan_GP/single_gp_summary.xlsx
+++ b/01_Thermal/B_results/Single_Fan_GP/single_gp_summary.xlsx
@@ -11,6 +11,7 @@
     <sheet name="per_sheet_metrics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="hyperparameters" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="single_gp_analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="autotune_cv" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,15 +475,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>kernel_family</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>alpha_scale</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>autotune_enabled</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>autotune_selected</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>use_radial_features</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>log_marginal_likelihood</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>kernel</t>
         </is>
@@ -493,22 +514,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03803914972487243</v>
+        <v>0.0302746793005408</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1187966915811342</v>
+        <v>0.1038145765542365</v>
       </c>
       <c r="D2" t="n">
-        <v>51.92343937445087</v>
+        <v>41.32493724523819</v>
       </c>
       <c r="E2" t="n">
-        <v>19.26377261530057</v>
+        <v>14.71124150650985</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06516331124277358</v>
+        <v>0.04922009667550305</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9601237314302804</v>
+        <v>0.9695475320944325</v>
       </c>
       <c r="H2" t="n">
         <v>1365</v>
@@ -518,15 +539,31 @@
           <t>polar</t>
         </is>
       </c>
-      <c r="J2" t="b">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>matern52_ard</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>polar_matern52</t>
+        </is>
+      </c>
+      <c r="N2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>-246.847471403069</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.23**2 * RBF(length_scale=[0.141, 3.97, 19.9, 0.288]) + WhiteKernel(noise_level=0.00664)</t>
+      <c r="O2" t="n">
+        <v>-231.0604936488842</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>1.27**2 * Matern(length_scale=[0.217, 3.91, 20.3, 0.405], nu=2.5) + WhiteKernel(noise_level=0.00242)</t>
         </is>
       </c>
     </row>
@@ -612,25 +649,25 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0272626215455659</v>
+        <v>0.0207876979836193</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07371661888439368</v>
+        <v>0.05559253227986779</v>
       </c>
       <c r="G2" t="n">
-        <v>5.316211201385351</v>
+        <v>4.053601106805763</v>
       </c>
       <c r="H2" t="n">
-        <v>1.059657280450655</v>
+        <v>0.6026532808311876</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05611123567304827</v>
+        <v>0.03842740224161371</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9896958999907943</v>
+        <v>0.9941398036977394</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07739825573960134</v>
+        <v>0.07108562846157999</v>
       </c>
     </row>
     <row r="3">
@@ -649,25 +686,25 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03666216046636091</v>
+        <v>0.02729688416446591</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1112256906938555</v>
+        <v>0.08793569795169277</v>
       </c>
       <c r="G3" t="n">
-        <v>7.149121290940379</v>
+        <v>5.322892412070852</v>
       </c>
       <c r="H3" t="n">
-        <v>2.412375082713418</v>
+        <v>1.507873959979012</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06264973332930582</v>
+        <v>0.04501581218634044</v>
       </c>
       <c r="J3" t="n">
-        <v>0.974528197767617</v>
+        <v>0.9840786502997932</v>
       </c>
       <c r="K3" t="n">
-        <v>0.07243483532147664</v>
+        <v>0.06547594306052759</v>
       </c>
     </row>
     <row r="4">
@@ -686,25 +723,25 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03563005653844309</v>
+        <v>0.02854897005864907</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1014877139362925</v>
+        <v>0.08598258455490122</v>
       </c>
       <c r="G4" t="n">
-        <v>6.947861024996403</v>
+        <v>5.567049161436568</v>
       </c>
       <c r="H4" t="n">
-        <v>2.008452435602874</v>
+        <v>1.441635945114444</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08172831157172519</v>
+        <v>0.06372834114267574</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9761786524812363</v>
+        <v>0.9829014069562447</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07309611938448095</v>
+        <v>0.06599496633929097</v>
       </c>
     </row>
     <row r="5">
@@ -723,25 +760,25 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04706414832257115</v>
+        <v>0.03745994961080077</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1547627704703274</v>
+        <v>0.1413849108605158</v>
       </c>
       <c r="G5" t="n">
-        <v>9.177508922901374</v>
+        <v>7.304690174106151</v>
       </c>
       <c r="H5" t="n">
-        <v>4.670545449111994</v>
+        <v>3.897990138712019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05704789313606046</v>
+        <v>0.039186544618123</v>
       </c>
       <c r="J5" t="n">
-        <v>0.931242814520278</v>
+        <v>0.9426159462774295</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06447368587794437</v>
+        <v>0.04892501457509677</v>
       </c>
     </row>
     <row r="6">
@@ -760,25 +797,25 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05209262101113771</v>
+        <v>0.04475753436351613</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1753198600162836</v>
+        <v>0.162784739372041</v>
       </c>
       <c r="G6" t="n">
-        <v>10.15806109717185</v>
+        <v>8.727719200885645</v>
       </c>
       <c r="H6" t="n">
-        <v>5.993725396645205</v>
+        <v>5.167279917622548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09796183476908378</v>
+        <v>0.08410877446406759</v>
       </c>
       <c r="J6" t="n">
-        <v>0.870169882860048</v>
+        <v>0.8880715227001634</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07044198382848003</v>
+        <v>0.05956535963697756</v>
       </c>
     </row>
     <row r="7">
@@ -797,25 +834,25 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03447844529976481</v>
+        <v>0.02748673631355905</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1049981771789993</v>
+        <v>0.08552352122441238</v>
       </c>
       <c r="G7" t="n">
-        <v>6.723296833454137</v>
+        <v>5.359913581144015</v>
       </c>
       <c r="H7" t="n">
-        <v>2.149800356127943</v>
+        <v>1.42628317311139</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08742295883459626</v>
+        <v>0.0672018369554928</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9577644068713045</v>
+        <v>0.9719788325394377</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08988010341484653</v>
+        <v>0.08529660691875755</v>
       </c>
     </row>
     <row r="8">
@@ -834,25 +871,25 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03308399489026344</v>
+        <v>0.02558498260917537</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07050064973872198</v>
+        <v>0.05850816691356773</v>
       </c>
       <c r="G8" t="n">
-        <v>6.451379003601372</v>
+        <v>4.989071608789196</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9692166146484824</v>
+        <v>0.6675250911392508</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04744876434512554</v>
+        <v>0.03594979591534166</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9730956121020226</v>
+        <v>0.9814702371872188</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06964840425919791</v>
+        <v>0.0581864002695555</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -956,11 +993,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>use_radial_features</t>
-        </is>
-      </c>
-      <c r="C7" t="b">
-        <v>0</v>
+          <t>kernel_family</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>matern52_ard</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -969,11 +1008,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sigma_fallback_mps</t>
+          <t>alpha_scale</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -982,11 +1021,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sigma_min_mps</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.03</v>
+          <t>autotune_enabled</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -995,11 +1034,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>n_restarts_optimizer</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>10</v>
+          <t>autotune_selected</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>polar_matern52</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1008,11 +1049,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>random_state</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>42</v>
+          <t>use_radial_features</t>
+        </is>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1021,12 +1062,90 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>sigma_fallback_mps</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sigma_min_mps</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>n_restarts_optimizer</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>random_state</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>autotune_cv_n_splits</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>autotune_cv_restarts_optimizer</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>kernel_fitted</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1.23**2 * RBF(length_scale=[0.141, 3.97, 19.9, 0.288]) + WhiteKernel(noise_level=0.00664)</t>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.27**2 * Matern(length_scale=[0.217, 3.91, 20.3, 0.405], nu=2.5) + WhiteKernel(noise_level=0.00242)</t>
         </is>
       </c>
     </row>
@@ -1099,16 +1218,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>5.316211201385351</v>
+        <v>4.053601106805763</v>
       </c>
       <c r="E2" t="n">
-        <v>1.059657280450655</v>
+        <v>0.6026532808311876</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05611123567304827</v>
+        <v>0.03842740224161371</v>
       </c>
       <c r="G2" t="n">
-        <v>37.7931427287662</v>
+        <v>17.7253734881638</v>
       </c>
       <c r="H2" t="n">
         <v>12003.65050354092</v>
@@ -1127,16 +1246,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>7.149121290940379</v>
+        <v>5.322892412070852</v>
       </c>
       <c r="E3" t="n">
-        <v>2.412375082713418</v>
+        <v>1.507873959979012</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06264973332930582</v>
+        <v>0.04501581218634044</v>
       </c>
       <c r="G3" t="n">
-        <v>38.47742745768466</v>
+        <v>19.86542016088185</v>
       </c>
       <c r="H3" t="n">
         <v>9803.193489796933</v>
@@ -1155,16 +1274,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>6.947861024996403</v>
+        <v>5.567049161436568</v>
       </c>
       <c r="E4" t="n">
-        <v>2.008452435602874</v>
+        <v>1.441635945114444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08172831157172519</v>
+        <v>0.06372834114267574</v>
       </c>
       <c r="G4" t="n">
-        <v>60.72327988049094</v>
+        <v>36.92116492278084</v>
       </c>
       <c r="H4" t="n">
         <v>9090.968804657296</v>
@@ -1183,16 +1302,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>9.177508922901374</v>
+        <v>7.304690174106151</v>
       </c>
       <c r="E5" t="n">
-        <v>4.670545449111994</v>
+        <v>3.897990138712019</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05704789313606046</v>
+        <v>0.039186544618123</v>
       </c>
       <c r="G5" t="n">
-        <v>233.1522670704965</v>
+        <v>110.0105568490274</v>
       </c>
       <c r="H5" t="n">
         <v>71640.79933933762</v>
@@ -1211,16 +1330,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>10.15806109717185</v>
+        <v>8.727719200885645</v>
       </c>
       <c r="E6" t="n">
-        <v>5.993725396645205</v>
+        <v>5.167279917622548</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09796183476908378</v>
+        <v>0.08410877446406759</v>
       </c>
       <c r="G6" t="n">
-        <v>153.9921851038078</v>
+        <v>113.5187160156764</v>
       </c>
       <c r="H6" t="n">
         <v>16046.66774128612</v>
@@ -1239,16 +1358,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>6.723296833454137</v>
+        <v>5.359913581144015</v>
       </c>
       <c r="E7" t="n">
-        <v>2.149800356127943</v>
+        <v>1.42628317311139</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08742295883459626</v>
+        <v>0.0672018369554928</v>
       </c>
       <c r="G7" t="n">
-        <v>41.30198358019971</v>
+        <v>24.40519020199147</v>
       </c>
       <c r="H7" t="n">
         <v>5404.056829595331</v>
@@ -1267,16 +1386,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>6.451379003601372</v>
+        <v>4.989071608789196</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9692166146484824</v>
+        <v>0.6675250911392508</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04744876434512554</v>
+        <v>0.03594979591534166</v>
       </c>
       <c r="G8" t="n">
-        <v>43.95807870632481</v>
+        <v>25.23374713228151</v>
       </c>
       <c r="H8" t="n">
         <v>19524.90314262348</v>
@@ -1293,19 +1412,330 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>51.92343937445087</v>
+        <v>41.32493724523819</v>
       </c>
       <c r="E9" t="n">
-        <v>19.26377261530057</v>
+        <v>14.71124150650985</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06516331124277359</v>
+        <v>0.04922009667550306</v>
       </c>
       <c r="G9" t="n">
-        <v>609.3983645277706</v>
+        <v>347.6801687708032</v>
       </c>
       <c r="H9" t="n">
         <v>143514.2398508377</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>feature_mode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_family</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>alpha_scale</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>n_folds</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cv_mae_mps</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>cv_rmse_mps</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>cv_wrmse_mps</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>cv_sae_mps</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cv_sse_mps2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cv_r2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>is_selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>polar_matern52</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>matern52_ard</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.09040535485436983</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2925370320382268</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2307671029392873</v>
+      </c>
+      <c r="J2" t="n">
+        <v>123.4033093762148</v>
+      </c>
+      <c r="K2" t="n">
+        <v>116.8138541302476</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.7581937498440972</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>polar_matern32</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>matern32_ard</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1412402662228938</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.372763861702857</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2551094906415324</v>
+      </c>
+      <c r="J3" t="n">
+        <v>192.79296339425</v>
+      </c>
+      <c r="K3" t="n">
+        <v>189.6707038475705</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6073790904058877</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>polar_rbf_high_alpha</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>rbf_ard</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1776876477822185</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4343581390077453</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2860247563312063</v>
+      </c>
+      <c r="J4" t="n">
+        <v>242.5436392227283</v>
+      </c>
+      <c r="K4" t="n">
+        <v>257.530445338901</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4669085122476531</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>polar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rbf_ard</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1844950904323686</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4594890153443723</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3114488586226459</v>
+      </c>
+      <c r="J5" t="n">
+        <v>251.8357984401832</v>
+      </c>
+      <c r="K5" t="n">
+        <v>288.1926618782222</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4034373113524699</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>radial_rbf</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>radial</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>rbf_ard</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1907882673077746</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4731128735095881</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3199938779649016</v>
+      </c>
+      <c r="J6" t="n">
+        <v>260.4259848751124</v>
+      </c>
+      <c r="K6" t="n">
+        <v>305.5358548248818</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3675366685444167</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/01_Thermal/B_results/Single_Fan_GP/single_gp_summary.xlsx
+++ b/01_Thermal/B_results/Single_Fan_GP/single_gp_summary.xlsx
@@ -514,34 +514,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0302746793005408</v>
+        <v>0.06333796008669042</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1038145765542365</v>
+        <v>0.2233251388500153</v>
       </c>
       <c r="D2" t="n">
-        <v>41.32493724523819</v>
+        <v>86.45631551833242</v>
       </c>
       <c r="E2" t="n">
-        <v>14.71124150650985</v>
+        <v>68.07817058184679</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04922009667550305</v>
+        <v>0.1673693214163189</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9695475320944325</v>
+        <v>0.8590772706847305</v>
       </c>
       <c r="H2" t="n">
         <v>1365</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>polar</t>
+          <t>cartesian</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>matern52_ard</t>
+          <t>matern32_ard</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,18 +552,18 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>polar_matern52</t>
+          <t>cartesian_matern32_ard_a1</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-231.0604936488842</v>
+        <v>-1017.82115185717</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1.27**2 * Matern(length_scale=[0.217, 3.91, 20.3, 0.405], nu=2.5) + WhiteKernel(noise_level=0.00242)</t>
+          <t>0.745**2 * Matern(length_scale=[0.164, 0.281, 7.72], nu=1.5) + WhiteKernel(noise_level=0.125)</t>
         </is>
       </c>
     </row>
@@ -649,25 +649,25 @@
         <v>195</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0207876979836193</v>
+        <v>0.09670396869947524</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05559253227986779</v>
+        <v>0.3418474121040082</v>
       </c>
       <c r="G2" t="n">
-        <v>4.053601106805763</v>
+        <v>18.85727389639767</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6026532808311876</v>
+        <v>22.78763236663048</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03842740224161371</v>
+        <v>0.4343216199199577</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9941398036977394</v>
+        <v>0.7784132216985151</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07108562846157999</v>
+        <v>0.2358083572520623</v>
       </c>
     </row>
     <row r="3">
@@ -686,25 +686,25 @@
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02729688416446591</v>
+        <v>0.07825331381793223</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08793569795169277</v>
+        <v>0.2519726439689836</v>
       </c>
       <c r="G3" t="n">
-        <v>5.322892412070852</v>
+        <v>15.25939619449679</v>
       </c>
       <c r="H3" t="n">
-        <v>1.507873959979012</v>
+        <v>12.38059159520043</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04501581218634044</v>
+        <v>0.1322751662198958</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9840786502997932</v>
+        <v>0.869275726277964</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06547594306052759</v>
+        <v>0.2326134955401947</v>
       </c>
     </row>
     <row r="4">
@@ -723,25 +723,25 @@
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02854897005864907</v>
+        <v>0.0813326684868258</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08598258455490122</v>
+        <v>0.3053131567905359</v>
       </c>
       <c r="G4" t="n">
-        <v>5.567049161436568</v>
+        <v>15.85987035493103</v>
       </c>
       <c r="H4" t="n">
-        <v>1.441635945114444</v>
+        <v>18.17714412333346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06372834114267574</v>
+        <v>0.3327705714836875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9829014069562447</v>
+        <v>0.7844091005667221</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06599496633929097</v>
+        <v>0.2303611671204477</v>
       </c>
     </row>
     <row r="5">
@@ -760,25 +760,25 @@
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03745994961080077</v>
+        <v>0.05066811691009252</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1413849108605158</v>
+        <v>0.1705436769363334</v>
       </c>
       <c r="G5" t="n">
-        <v>7.304690174106151</v>
+        <v>9.880282797468041</v>
       </c>
       <c r="H5" t="n">
-        <v>3.897990138712019</v>
+        <v>5.67160341987807</v>
       </c>
       <c r="I5" t="n">
-        <v>0.039186544618123</v>
+        <v>0.06497447137683202</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9426159462774295</v>
+        <v>0.9165057930477637</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04892501457509677</v>
+        <v>0.2285264888023534</v>
       </c>
     </row>
     <row r="6">
@@ -797,25 +797,25 @@
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04475753436351613</v>
+        <v>0.05744526064084968</v>
       </c>
       <c r="F6" t="n">
-        <v>0.162784739372041</v>
+        <v>0.1587549071646715</v>
       </c>
       <c r="G6" t="n">
-        <v>8.727719200885645</v>
+        <v>11.20182582496569</v>
       </c>
       <c r="H6" t="n">
-        <v>5.167279917622548</v>
+        <v>4.914608507028374</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08410877446406759</v>
+        <v>0.100018362759265</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8880715227001634</v>
+        <v>0.8935446394455051</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05956535963697756</v>
+        <v>0.2292473242389486</v>
       </c>
     </row>
     <row r="7">
@@ -834,25 +834,25 @@
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02748673631355905</v>
+        <v>0.03919203842761308</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08552352122441238</v>
+        <v>0.1154390188055789</v>
       </c>
       <c r="G7" t="n">
-        <v>5.359913581144015</v>
+        <v>7.642447493384552</v>
       </c>
       <c r="H7" t="n">
-        <v>1.42628317311139</v>
+        <v>2.598602577244985</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0672018369554928</v>
+        <v>0.1081373533909287</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9719788325394377</v>
+        <v>0.9489471099756545</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08529660691875755</v>
+        <v>0.2352422753694616</v>
       </c>
     </row>
     <row r="8">
@@ -871,25 +871,25 @@
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02558498260917537</v>
+        <v>0.0397703536240444</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05850816691356773</v>
+        <v>0.08909769896971217</v>
       </c>
       <c r="G8" t="n">
-        <v>4.989071608789196</v>
+        <v>7.755218956688658</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6675250911392508</v>
+        <v>1.547987992531003</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03594979591534166</v>
+        <v>0.05135420700183138</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9814702371872188</v>
+        <v>0.9570295548146682</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0581864002695555</v>
+        <v>0.2494849709848093</v>
       </c>
     </row>
   </sheetData>
@@ -983,7 +983,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>polar</t>
+          <t>cartesian</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>matern52_ard</t>
+          <t>matern32_ard</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>polar_matern52</t>
+          <t>cartesian_matern32_ard_a1</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.27**2 * Matern(length_scale=[0.217, 3.91, 20.3, 0.405], nu=2.5) + WhiteKernel(noise_level=0.00242)</t>
+          <t>0.745**2 * Matern(length_scale=[0.164, 0.281, 7.72], nu=1.5) + WhiteKernel(noise_level=0.125)</t>
         </is>
       </c>
     </row>
@@ -1218,16 +1218,16 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>4.053601106805763</v>
+        <v>18.85727389639767</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6026532808311876</v>
+        <v>22.78763236663048</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03842740224161371</v>
+        <v>0.4343216199199577</v>
       </c>
       <c r="G2" t="n">
-        <v>17.7253734881638</v>
+        <v>2264.311848078115</v>
       </c>
       <c r="H2" t="n">
         <v>12003.65050354092</v>
@@ -1246,16 +1246,16 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>5.322892412070852</v>
+        <v>15.25939619449679</v>
       </c>
       <c r="E3" t="n">
-        <v>1.507873959979012</v>
+        <v>12.38059159520043</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04501581218634044</v>
+        <v>0.1322751662198958</v>
       </c>
       <c r="G3" t="n">
-        <v>19.86542016088185</v>
+        <v>171.523727660828</v>
       </c>
       <c r="H3" t="n">
         <v>9803.193489796933</v>
@@ -1274,16 +1274,16 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>5.567049161436568</v>
+        <v>15.85987035493103</v>
       </c>
       <c r="E4" t="n">
-        <v>1.441635945114444</v>
+        <v>18.17714412333346</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06372834114267574</v>
+        <v>0.3327705714836875</v>
       </c>
       <c r="G4" t="n">
-        <v>36.92116492278084</v>
+        <v>1006.699823800198</v>
       </c>
       <c r="H4" t="n">
         <v>9090.968804657296</v>
@@ -1302,16 +1302,16 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>7.304690174106151</v>
+        <v>9.880282797468041</v>
       </c>
       <c r="E5" t="n">
-        <v>3.897990138712019</v>
+        <v>5.67160341987807</v>
       </c>
       <c r="F5" t="n">
-        <v>0.039186544618123</v>
+        <v>0.06497447137683202</v>
       </c>
       <c r="G5" t="n">
-        <v>110.0105568490274</v>
+        <v>302.4446680716975</v>
       </c>
       <c r="H5" t="n">
         <v>71640.79933933762</v>
@@ -1330,16 +1330,16 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>8.727719200885645</v>
+        <v>11.20182582496569</v>
       </c>
       <c r="E6" t="n">
-        <v>5.167279917622548</v>
+        <v>4.914608507028374</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08410877446406759</v>
+        <v>0.100018362759265</v>
       </c>
       <c r="G6" t="n">
-        <v>113.5187160156764</v>
+        <v>160.5256150429997</v>
       </c>
       <c r="H6" t="n">
         <v>16046.66774128612</v>
@@ -1358,16 +1358,16 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>5.359913581144015</v>
+        <v>7.642447493384552</v>
       </c>
       <c r="E7" t="n">
-        <v>1.42628317311139</v>
+        <v>2.598602577244985</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0672018369554928</v>
+        <v>0.1081373533909287</v>
       </c>
       <c r="G7" t="n">
-        <v>24.40519020199147</v>
+        <v>63.19335016763585</v>
       </c>
       <c r="H7" t="n">
         <v>5404.056829595331</v>
@@ -1386,16 +1386,16 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>4.989071608789196</v>
+        <v>7.755218956688658</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6675250911392508</v>
+        <v>1.547987992531003</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03594979591534166</v>
+        <v>0.05135420700183138</v>
       </c>
       <c r="G8" t="n">
-        <v>25.23374713228151</v>
+        <v>51.49214017420562</v>
       </c>
       <c r="H8" t="n">
         <v>19524.90314262348</v>
@@ -1412,16 +1412,16 @@
         <v>1365</v>
       </c>
       <c r="D9" t="n">
-        <v>41.32493724523819</v>
+        <v>86.45631551833245</v>
       </c>
       <c r="E9" t="n">
-        <v>14.71124150650985</v>
+        <v>68.07817058184681</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04922009667550306</v>
+        <v>0.1673693214163189</v>
       </c>
       <c r="G9" t="n">
-        <v>347.6801687708032</v>
+        <v>4020.191172995679</v>
       </c>
       <c r="H9" t="n">
         <v>143514.2398508377</v>
@@ -1438,7 +1438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>polar_matern52</t>
+          <t>cartesian_matern32_ard_a1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>polar</t>
+          <t>cartesian</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>matern52_ard</t>
+          <t>matern32_ard</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1529,22 +1529,22 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09040535485436983</v>
+        <v>0.08654992575434997</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2925370320382268</v>
+        <v>0.3065748162337977</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2307671029392873</v>
+        <v>0.2318532585217923</v>
       </c>
       <c r="J2" t="n">
-        <v>123.4033093762148</v>
+        <v>118.1406486546877</v>
       </c>
       <c r="K2" t="n">
-        <v>116.8138541302476</v>
+        <v>128.293781000094</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7581937498440972</v>
+        <v>0.7344301467241592</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -1552,21 +1552,21 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>polar_matern32</t>
+          <t>cartesian_matern52_ard_a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>polar</t>
+          <t>cartesian</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>matern32_ard</t>
+          <t>matern52_ard</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1576,22 +1576,22 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1412402662228938</v>
+        <v>0.08729921420779697</v>
       </c>
       <c r="H3" t="n">
-        <v>0.372763861702857</v>
+        <v>0.3081778045456318</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2551094906415324</v>
+        <v>0.2327178731644629</v>
       </c>
       <c r="J3" t="n">
-        <v>192.79296339425</v>
+        <v>119.1634273936429</v>
       </c>
       <c r="K3" t="n">
-        <v>189.6707038475705</v>
+        <v>129.6389083278821</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6073790904058877</v>
+        <v>0.7316457150526213</v>
       </c>
       <c r="M3" t="b">
         <v>0</v>
@@ -1599,16 +1599,16 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>polar_rbf_high_alpha</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>polar</t>
+          <t>cartesian</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1617,28 +1617,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1776876477822185</v>
+        <v>0.08819789356732359</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4343581390077453</v>
+        <v>0.3094869793039827</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2860247563312063</v>
+        <v>0.2335596382134308</v>
       </c>
       <c r="J4" t="n">
-        <v>242.5436392227283</v>
+        <v>120.3901247193967</v>
       </c>
       <c r="K4" t="n">
-        <v>257.530445338901</v>
+        <v>130.7426898396307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4669085122476531</v>
+        <v>0.7293608724683696</v>
       </c>
       <c r="M4" t="b">
         <v>0</v>
@@ -1646,46 +1646,46 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>cartesian_matern32_ard_a1p3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>polar</t>
+          <t>cartesian</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rbf_ard</t>
+          <t>matern32_ard</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1844950904323686</v>
+        <v>0.08693926081496706</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4594890153443723</v>
+        <v>0.3111994446192519</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3114488586226459</v>
+        <v>0.237323751503257</v>
       </c>
       <c r="J5" t="n">
-        <v>251.8357984401832</v>
+        <v>118.67209101243</v>
       </c>
       <c r="K5" t="n">
-        <v>288.1926618782222</v>
+        <v>132.1935537622666</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4034373113524699</v>
+        <v>0.7263575646224707</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -1693,48 +1693,95 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>radial_rbf</t>
+          <t>cartesian_matern52_ard_a1p3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>radial</t>
+          <t>cartesian</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rbf_ard</t>
+          <t>matern52_ard</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1907882673077746</v>
+        <v>0.08745498858630829</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4731128735095881</v>
+        <v>0.3117269073419795</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3199938779649016</v>
+        <v>0.2377714507897196</v>
       </c>
       <c r="J6" t="n">
-        <v>260.4259848751124</v>
+        <v>119.3760594203108</v>
       </c>
       <c r="K6" t="n">
-        <v>305.5358548248818</v>
+        <v>132.6420523987583</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3675366685444167</v>
+        <v>0.7254291664089406</v>
       </c>
       <c r="M6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cartesian_rbf_ard_a1p3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cartesian</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>rbf_ard</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.09046638755421683</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3241282379758567</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2415336638057015</v>
+      </c>
+      <c r="J7" t="n">
+        <v>123.486619011506</v>
+      </c>
+      <c r="K7" t="n">
+        <v>143.4056915018003</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7031482886062443</v>
+      </c>
+      <c r="M7" t="b">
         <v>0</v>
       </c>
     </row>
